--- a/DOSSIES_MULTIFORMATO/ARSEPAM/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/ARSEPAM/dossie.xlsx
@@ -636,7 +636,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2020NE00406</t>
+          <t>2020NE00407</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7.34</v>
+        <v>8.16</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -655,14 +655,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA 2020NE0011, EM ATENÇÃO AO DECRETO Nº 43.042 DE 18/11/2020 REFERENTE AO ENCERRAMENTO DA EXECUÇÃO ORÇAMENTÁRIA, FINANCEIRA E CONTÁBIL DO EXERCÍCIO DE 2020.</t>
+          <t>ANULAÇÃO DO SALDO DA 2020NE0033, EM ATENÇÃO AO DECRETO Nº 43.042 DE 18/11/2020 REFERENTE AO ENCERRAMENTO DA EXECUÇÃO ORÇAMENTÁRIA, FINANCEIRA E CONTÁBIL DO EXERCÍCIO DE 2020.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2020NE00407</t>
+          <t>2020NE00406</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8.16</v>
+        <v>7.34</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA 2020NE0033, EM ATENÇÃO AO DECRETO Nº 43.042 DE 18/11/2020 REFERENTE AO ENCERRAMENTO DA EXECUÇÃO ORÇAMENTÁRIA, FINANCEIRA E CONTÁBIL DO EXERCÍCIO DE 2020.</t>
+          <t>ANULAÇÃO DO SALDO DA 2020NE0011, EM ATENÇÃO AO DECRETO Nº 43.042 DE 18/11/2020 REFERENTE AO ENCERRAMENTO DA EXECUÇÃO ORÇAMENTÁRIA, FINANCEIRA E CONTÁBIL DO EXERCÍCIO DE 2020.</t>
         </is>
       </c>
     </row>
@@ -718,12 +718,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2020NE00100</t>
+          <t>2020NE00095</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12/2018</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11693.25</v>
+        <v>67499.10000000001</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Contratação de Prestação de Serviços de Sistema de Protocolo em Plataforma Web - SPROWEB.</t>
+          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE ACESSO A REDE MUNDIAL DE COMPUTADORES (INTERNET) - Contrato nº. 001/2018 (2º Termo Aditivo)</t>
         </is>
       </c>
     </row>
@@ -778,12 +778,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2020NE00095</t>
+          <t>2020NE00100</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>12/2018</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>67499.10000000001</v>
+        <v>11693.25</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -801,14 +801,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE ACESSO A REDE MUNDIAL DE COMPUTADORES (INTERNET) - Contrato nº. 001/2018 (2º Termo Aditivo)</t>
+          <t>Contratação de Prestação de Serviços de Sistema de Protocolo em Plataforma Web - SPROWEB.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2020NE00352</t>
+          <t>2020NE00351</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1105.59</v>
+        <v>84.81</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -827,14 +827,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anulação do Saldo da Nota de Empenho nº. 2020NE00099 Motivo: Tendo em vista que as faturas/notas fiscais referente a prestação de serviços de execução do sistema PRODAM RH, foram emitidas, atestadas e</t>
+          <t>Anulação do Saldo da Nota de Empenho nº. 2020NE00030 Motivo: Tendo em vista que as faturas/notas fiscais referente a prestação de serviços de execução do sistema PRODAM RH, foram emitidas, atestadas e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2020NE00351</t>
+          <t>2020NE00352</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>84.81</v>
+        <v>1105.59</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -853,19 +853,19 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Anulação do Saldo da Nota de Empenho nº. 2020NE00030 Motivo: Tendo em vista que as faturas/notas fiscais referente a prestação de serviços de execução do sistema PRODAM RH, foram emitidas, atestadas e</t>
+          <t>Anulação do Saldo da Nota de Empenho nº. 2020NE00099 Motivo: Tendo em vista que as faturas/notas fiscais referente a prestação de serviços de execução do sistema PRODAM RH, foram emitidas, atestadas e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2015NE00090</t>
+          <t>2015NE00089</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12/2012</t>
+          <t>6/2014</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6285.28</v>
+        <v>67080</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -883,19 +883,19 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>01- ANULAÇÃO TOTAL DA NE Nº 010 MOTIVO EXTINÇÃO DA UG 025201, DATA DE 30/03/2015, SENDO SUBSTITUIDA PELA 11209 CONFORME LEI COMPLEMENTAR Nº 152 DE 09/03/2015.</t>
+          <t>01- ANULAÇÃO TOTAL DA NE Nº 006 MOTIVO EXTINÇÃO DA UG 025201, DATA DE 30/03/2015, SENDO SUBSTITUIDA PELA 11209 CONFORME LEI COMPLEMENTAR Nº 152 DE 09/03/2015.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2015NE00089</t>
+          <t>2015NE00090</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6/2014</t>
+          <t>12/2012</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>67080</v>
+        <v>6285.28</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -913,14 +913,14 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>01- ANULAÇÃO TOTAL DA NE Nº 006 MOTIVO EXTINÇÃO DA UG 025201, DATA DE 30/03/2015, SENDO SUBSTITUIDA PELA 11209 CONFORME LEI COMPLEMENTAR Nº 152 DE 09/03/2015.</t>
+          <t>01- ANULAÇÃO TOTAL DA NE Nº 010 MOTIVO EXTINÇÃO DA UG 025201, DATA DE 30/03/2015, SENDO SUBSTITUIDA PELA 11209 CONFORME LEI COMPLEMENTAR Nº 152 DE 09/03/2015.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2017NE00426</t>
+          <t>2017NE00425</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1477.66</v>
+        <v>1794.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2017NE00425</t>
+          <t>2017NE00426</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1794.1</v>
+        <v>1477.66</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2016NE00425</t>
+          <t>2016NE00424</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>355.11</v>
+        <v>869.85</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2016NE00424</t>
+          <t>2016NE00425</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>869.85</v>
+        <v>355.11</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1050,12 +1050,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2022NE0000412</t>
+          <t>2022NE0000406</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12/2018</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2335.68</v>
+        <v>4350.22</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1073,19 +1073,19 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB). REF. MESES DE SETEMBRO E OUTUBRO - CONTRATO N. 012/2018 (3º TA).</t>
+          <t>Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação - GERWEB - Gestor de Conteúdo Web.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2022NE0000406</t>
+          <t>2022NE0000412</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>12/2018</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1094,7 +1094,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4350.22</v>
+        <v>2335.68</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação - GERWEB - Gestor de Conteúdo Web.</t>
+          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB). REF. MESES DE SETEMBRO E OUTUBRO - CONTRATO N. 012/2018 (3º TA).</t>
         </is>
       </c>
     </row>
@@ -1170,12 +1170,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2019NE00164</t>
+          <t>2019NE00166</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>12/2018</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1184,7 +1184,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5685.85</v>
+        <v>11589.31</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Empenho complementar para suprir a despesa Referente a Prestação de Serviço de folha de pagamento pessoal - PRODAM - RH</t>
+          <t>Contratação de Prestação de Serviços de PROTOCOLO em Sistema de Plataforma SPROWEB.</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1230,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2019NE00166</t>
+          <t>2019NE00164</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12/2018</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11589.31</v>
+        <v>5685.85</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1253,14 +1253,14 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Contratação de Prestação de Serviços de PROTOCOLO em Sistema de Plataforma SPROWEB.</t>
+          <t>Empenho complementar para suprir a despesa Referente a Prestação de Serviço de folha de pagamento pessoal - PRODAM - RH</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2023NE0000438</t>
+          <t>2023NE0000434</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1270,7 +1270,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1.35</v>
+        <v>735</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NOTA DE EMPENHO Nº. 2023NE000361. EM CUMPRIMENTO AO ESTABELECIDO NO DECRETO Nº. 48.363 DE 27 DE OUTUBRO DE 2023.</t>
+          <t>ANULAÇÃO DO SALDO DA NOTA DE EMPENHO Nº. 2023NE0009. EM CUMPRIMENTO AO ESTABELECIDO NO DECRETO Nº. 48.363 DE 27 DE OUTUBRO DE 2023.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2023NE0000434</t>
+          <t>2023NE0000438</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1296,7 +1296,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>735</v>
+        <v>1.35</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1305,14 +1305,14 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NOTA DE EMPENHO Nº. 2023NE0009. EM CUMPRIMENTO AO ESTABELECIDO NO DECRETO Nº. 48.363 DE 27 DE OUTUBRO DE 2023.</t>
+          <t>ANULAÇÃO DO SALDO DA NOTA DE EMPENHO Nº. 2023NE000361. EM CUMPRIMENTO AO ESTABELECIDO NO DECRETO Nº. 48.363 DE 27 DE OUTUBRO DE 2023.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2022NE0000622</t>
+          <t>2022NE0000621</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>706.89</v>
+        <v>2529.01</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1331,14 +1331,14 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NOTA DE EMPENHO Nº 2022NE00000517 5º ADITIVO AO CONTRATO Nº 003/2017 - ARSEPAM; OBJETO: CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS REFERENTE A EXECUÇÃO DE SISTEMA DE CADASTRO DE FOLHA DE PAGAMEN</t>
+          <t>ANULAÇÃO DA NOTA DE EMPENHO Nº 2022NE00000517 5º ADITIVO AO CONTRATO Nº 01/2018 - ARSEPAM; OBJETO: CONTRATAÇÃO PARA PRESTAÇÃO DE SERVIÇO DE FORNECIMENTO DE CIRCUITO DE TRANSMISSÃO DE DADOS (INTERNET);</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2022NE0000608</t>
+          <t>2022NE0000611</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>734.5</v>
+        <v>38.94</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1357,14 +1357,14 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NOTA DE EMPENHO Nº 2022NE0000130 5º TERMO ADITIVO AO CONTRATO Nº 001/2018 - ARSEPAM; OBJETO: CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE ACESSO À INTERNET BANDA LARG</t>
+          <t xml:space="preserve">ANULAÇÃO DA NOTA DE EMPENHO Nº 2022NE00000470 3º ADITIVO AO CONTRATO Nº 012/2018 - ARSEPAM; OBJETO: CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMA DE PROTOCOLO EM PLATAFORMA </t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2022NE0000611</t>
+          <t>2022NE0000608</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>38.94</v>
+        <v>734.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1383,14 +1383,14 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANULAÇÃO DA NOTA DE EMPENHO Nº 2022NE00000470 3º ADITIVO AO CONTRATO Nº 012/2018 - ARSEPAM; OBJETO: CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMA DE PROTOCOLO EM PLATAFORMA </t>
+          <t>ANULAÇÃO DA NOTA DE EMPENHO Nº 2022NE0000130 5º TERMO ADITIVO AO CONTRATO Nº 001/2018 - ARSEPAM; OBJETO: CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE ACESSO À INTERNET BANDA LARG</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2022NE0000621</t>
+          <t>2022NE0000622</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2529.01</v>
+        <v>706.89</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1409,14 +1409,14 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NOTA DE EMPENHO Nº 2022NE00000517 5º ADITIVO AO CONTRATO Nº 01/2018 - ARSEPAM; OBJETO: CONTRATAÇÃO PARA PRESTAÇÃO DE SERVIÇO DE FORNECIMENTO DE CIRCUITO DE TRANSMISSÃO DE DADOS (INTERNET);</t>
+          <t>ANULAÇÃO DA NOTA DE EMPENHO Nº 2022NE00000517 5º ADITIVO AO CONTRATO Nº 003/2017 - ARSEPAM; OBJETO: CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS REFERENTE A EXECUÇÃO DE SISTEMA DE CADASTRO DE FOLHA DE PAGAMEN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2018NE00478</t>
+          <t>2018NE00508</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>219.73</v>
+        <v>5844.7</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1435,14 +1435,14 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NE Nº 00018, DE ACORDO COM INSTRUÇÃO NORMATIVA Nº 01/2018/SET/SEFAZ, DE 30 DE NOVEMBRO DE 2018. MOTIVO: ENCERRAMENTO DE EXERCÍCIO DE 2018.</t>
+          <t>CANCELAMENTO PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI FEDERAL Nº 101/2000 ( LEI DE RESPONSABILIDADE FISCAL).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2018NE00494</t>
+          <t>2018NE00503</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1950.18</v>
+        <v>2737.83</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2018NE00503</t>
+          <t>2018NE00494</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1478,7 +1478,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2737.83</v>
+        <v>1950.18</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2018NE00508</t>
+          <t>2018NE00478</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>5844.7</v>
+        <v>219.73</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CANCELAMENTO PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI FEDERAL Nº 101/2000 ( LEI DE RESPONSABILIDADE FISCAL).</t>
+          <t>ANULAÇÃO DO SALDO DA NE Nº 00018, DE ACORDO COM INSTRUÇÃO NORMATIVA Nº 01/2018/SET/SEFAZ, DE 30 DE NOVEMBRO DE 2018. MOTIVO: ENCERRAMENTO DE EXERCÍCIO DE 2018.</t>
         </is>
       </c>
     </row>
@@ -1576,10 +1576,14 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2022NE0000037</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
+          <t>2022NE0000036</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>4/2021</t>
+        </is>
+      </c>
       <c r="C36" t="inlineStr">
         <is>
           <t>28/01/2022</t>
@@ -1595,21 +1599,17 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Anulação da nota de empenho 2022NE0000036 Motivo: Erro formal de processamento.</t>
+          <t>Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação - GERWEB - Gestor de Conteúdo Web.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2022NE0000036</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>4/2021</t>
-        </is>
-      </c>
+          <t>2022NE0000037</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
           <t>28/01/2022</t>
@@ -1625,14 +1625,14 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação - GERWEB - Gestor de Conteúdo Web.</t>
+          <t>Anulação da nota de empenho 2022NE0000036 Motivo: Erro formal de processamento.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2024NE0000687</t>
+          <t>2024NE0000686</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2169.1</v>
+        <v>2614.39</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Anulação de saldo da Nota de Empenho 2024NE0000088; Motivo: Considerando autorização Diretor Administrativo e Financeiro, fl. 8 do Memorando nº 009/2024-DEFIN/ARSEPAM e encerramento do exercício finan</t>
+          <t>Anulação de saldo da Nota de Empenho 2024NE0000005; Motivo: Considerando autorização Diretor Administrativo e Financeiro, fl. 8 do Memorando nº 009/2024-DEFIN/ARSEPAM e encerramento do exercício finan</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2024NE0000686</t>
+          <t>2024NE0000687</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2614.39</v>
+        <v>2169.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Anulação de saldo da Nota de Empenho 2024NE0000005; Motivo: Considerando autorização Diretor Administrativo e Financeiro, fl. 8 do Memorando nº 009/2024-DEFIN/ARSEPAM e encerramento do exercício finan</t>
+          <t>Anulação de saldo da Nota de Empenho 2024NE0000088; Motivo: Considerando autorização Diretor Administrativo e Financeiro, fl. 8 do Memorando nº 009/2024-DEFIN/ARSEPAM e encerramento do exercício finan</t>
         </is>
       </c>
     </row>
@@ -1770,12 +1770,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025NE0000075</t>
+          <t>2025NE0000074</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2215.57</v>
+        <v>2458.35</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1793,19 +1793,19 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação Gestor de Conteúdo Web para atender as necessidades da Agência Reguladora de Serviços Públicos </t>
+          <t>CONTRATAÇÃO DOS SERVIÇOS DE EXECUÇÃO DO SISTEMA PRODAM-RH PARA O CONTROLE DE CADASTRO DE PESSOAL, PROCESSAMENTO DE FOLHA DE PAGAMENTO E TRANSMISSÃO DE DADOS PARA O E-SOCIAL PARA ATENDER AS NECESSIDADE</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025NE0000074</t>
+          <t>2025NE0000075</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2458.35</v>
+        <v>2215.57</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DOS SERVIÇOS DE EXECUÇÃO DO SISTEMA PRODAM-RH PARA O CONTROLE DE CADASTRO DE PESSOAL, PROCESSAMENTO DE FOLHA DE PAGAMENTO E TRANSMISSÃO DE DADOS PARA O E-SOCIAL PARA ATENDER AS NECESSIDADE</t>
+          <t xml:space="preserve">Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação Gestor de Conteúdo Web para atender as necessidades da Agência Reguladora de Serviços Públicos </t>
         </is>
       </c>
     </row>
@@ -1890,12 +1890,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2021NE0000061</t>
+          <t>2021NE0000060</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>12/2018</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>14367.28</v>
+        <v>40519.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Contratação de Prestação de Serviços de protocolo em sistema de plataforma web - SPROWEB.</t>
+          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE ACESSO A REDE MUNDIAL DE COMPUTADORES (INTERNET)</t>
         </is>
       </c>
     </row>
@@ -1950,12 +1950,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2021NE0000060</t>
+          <t>2021NE0000061</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>12/2018</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>40519.8</v>
+        <v>14367.28</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1973,28 +1973,24 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE ACESSO A REDE MUNDIAL DE COMPUTADORES (INTERNET)</t>
+          <t>Contratação de Prestação de Serviços de protocolo em sistema de plataforma web - SPROWEB.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2022NE0000556</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>12/2018</t>
-        </is>
-      </c>
+          <t>2022NE0000553</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
           <t>25/11/2022</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1268.16</v>
+        <v>62.04</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2003,24 +1999,28 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB). Contrato Nº 012/2018 (4º TA).</t>
+          <t>Anulação parcial da Nota de empenho - NE nº. 2022NE000517 Motivo: Encerramento do Exercício</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2022NE0000553</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
+          <t>2022NE0000556</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>12/2018</t>
+        </is>
+      </c>
       <c r="C51" t="inlineStr">
         <is>
           <t>25/11/2022</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>62.04</v>
+        <v>1268.16</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2029,19 +2029,19 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Anulação parcial da Nota de empenho - NE nº. 2022NE000517 Motivo: Encerramento do Exercício</t>
+          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB). Contrato Nº 012/2018 (4º TA).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2025NE0000343</t>
+          <t>2025NE0000342</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2458.35</v>
+        <v>2402.56</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2059,19 +2059,19 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DOS SERVIÇOS DE EXECUÇÃO DO SISTEMA PRODAM-RH PARA O CONTROLE DE CADASTRO DE PESSOAL, PROCESSAMENTO DE FOLHA DE PAGAMENTO E TRANSMISSÃO DE DADOS PARA O E-SOCIAL PARA ATENDER AS NECESSIDADE</t>
+          <t xml:space="preserve">Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação Gestor de Conteúdo Web para atender as necessidades da Agência Reguladora de Serviços Públicos </t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2025NE0000342</t>
+          <t>2025NE0000343</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2402.56</v>
+        <v>2458.35</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2089,14 +2089,14 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação Gestor de Conteúdo Web para atender as necessidades da Agência Reguladora de Serviços Públicos </t>
+          <t>CONTRATAÇÃO DOS SERVIÇOS DE EXECUÇÃO DO SISTEMA PRODAM-RH PARA O CONTROLE DE CADASTRO DE PESSOAL, PROCESSAMENTO DE FOLHA DE PAGAMENTO E TRANSMISSÃO DE DADOS PARA O E-SOCIAL PARA ATENDER AS NECESSIDADE</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2025NE0000561</t>
+          <t>2025NE0000555</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>6.24</v>
+        <v>9651.709999999999</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2115,14 +2115,14 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anulação do saldo da nota de empenho nº. 0203/2025 Em atenção as normas e procedimentos do Decreto nº. 52.770 de 21/10/2025 - Encerramento da execução orçamentária, financeira, patrimonial e contábil </t>
+          <t>Anulação do saldo da nota de empenho nº. 0006/2025 Contrato nº. 006/2024 (1ºTA) Em atenção as normas e procedimentos do Decreto nº. 52.770 de 21/10/2025 - Encerramento da execução orçamentária, financ</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2025NE0000555</t>
+          <t>2025NE0000561</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>9651.709999999999</v>
+        <v>6.24</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2141,19 +2141,19 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Anulação do saldo da nota de empenho nº. 0006/2025 Contrato nº. 006/2024 (1ºTA) Em atenção as normas e procedimentos do Decreto nº. 52.770 de 21/10/2025 - Encerramento da execução orçamentária, financ</t>
+          <t xml:space="preserve">Anulação do saldo da nota de empenho nº. 0203/2025 Em atenção as normas e procedimentos do Decreto nº. 52.770 de 21/10/2025 - Encerramento da execução orçamentária, financeira, patrimonial e contábil </t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2022NE0000548</t>
+          <t>2022NE0000541</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2175.11</v>
+        <v>1789.07</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2171,19 +2171,19 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação - GERWEB - Gestor de Conteúdo Web. Contrato Nº 004/2021 (1º TA).</t>
+          <t>Contratação de Empresa especializada na prestação de serviços de execução de Sistema de Recursos Humanos e Cadastro de Folha de Pagamento de Pessoal - PRODAM-RH; CT 003/2017 (5º TA).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2022NE0000541</t>
+          <t>2022NE0000548</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1789.07</v>
+        <v>2175.11</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2201,19 +2201,19 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Contratação de Empresa especializada na prestação de serviços de execução de Sistema de Recursos Humanos e Cadastro de Folha de Pagamento de Pessoal - PRODAM-RH; CT 003/2017 (5º TA).</t>
+          <t>Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação - GERWEB - Gestor de Conteúdo Web. Contrato Nº 004/2021 (1º TA).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2025NE0000147</t>
+          <t>2025NE0000148</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2222,7 +2222,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2458.35</v>
+        <v>2215.57</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2231,19 +2231,19 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DOS SERVIÇOS DE EXECUÇÃO DO SISTEMA PRODAM-RH PARA O CONTROLE DE CADASTRO DE PESSOAL, PROCESSAMENTO DE FOLHA DE PAGAMENTO E TRANSMISSÃO DE DADOS PARA O E-SOCIAL PARA ATENDER AS NECESSIDADE</t>
+          <t xml:space="preserve">Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação Gestor de Conteúdo Web para atender as necessidades da Agência Reguladora de Serviços Públicos </t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2025NE0000148</t>
+          <t>2025NE0000147</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2215.57</v>
+        <v>2458.35</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação Gestor de Conteúdo Web para atender as necessidades da Agência Reguladora de Serviços Públicos </t>
+          <t>CONTRATAÇÃO DOS SERVIÇOS DE EXECUÇÃO DO SISTEMA PRODAM-RH PARA O CONTROLE DE CADASTRO DE PESSOAL, PROCESSAMENTO DE FOLHA DE PAGAMENTO E TRANSMISSÃO DE DADOS PARA O E-SOCIAL PARA ATENDER AS NECESSIDADE</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2022NE0000319</t>
+          <t>2022NE0000320</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2454,7 +2454,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>522.11</v>
+        <v>1895.19</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Anulação do Saldo da nota de empenho nº. 2022NE000052. Contrato nº. 001/2018 (5º TA) - ARSEPAM, referente a Contratação de prestação de serviço de fornecimento de circuito de transmissão de dados (INT</t>
+          <t>Anulação do Saldo da nota de empenho nº. 2022NE000139. Contrato nº. 004/2021-ARSEPAM. Objeto: Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação -</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2500,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2022NE0000320</t>
+          <t>2022NE0000319</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1895.19</v>
+        <v>522.11</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Anulação do Saldo da nota de empenho nº. 2022NE000139. Contrato nº. 004/2021-ARSEPAM. Objeto: Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação -</t>
+          <t>Anulação do Saldo da nota de empenho nº. 2022NE000052. Contrato nº. 001/2018 (5º TA) - ARSEPAM, referente a Contratação de prestação de serviço de fornecimento de circuito de transmissão de dados (INT</t>
         </is>
       </c>
     </row>
@@ -2586,12 +2586,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025NE0000375</t>
+          <t>2025NE0000376</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2600,7 +2600,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2402.56</v>
+        <v>2458.35</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2609,19 +2609,19 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação Gestor de Conteúdo Web para atender as necessidades da Agência Reguladora de Serviços Públicos </t>
+          <t>CONTRATAÇÃO DOS SERVIÇOS DE EXECUÇÃO DO SISTEMA PRODAM-RH PARA O CONTROLE DE CADASTRO DE PESSOAL, PROCESSAMENTO DE FOLHA DE PAGAMENTO E TRANSMISSÃO DE DADOS PARA O E-SOCIAL PARA ATENDER AS NECESSIDADE</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025NE0000376</t>
+          <t>2025NE0000375</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>2458.35</v>
+        <v>2402.56</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DOS SERVIÇOS DE EXECUÇÃO DO SISTEMA PRODAM-RH PARA O CONTROLE DE CADASTRO DE PESSOAL, PROCESSAMENTO DE FOLHA DE PAGAMENTO E TRANSMISSÃO DE DADOS PARA O E-SOCIAL PARA ATENDER AS NECESSIDADE</t>
+          <t xml:space="preserve">Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação Gestor de Conteúdo Web para atender as necessidades da Agência Reguladora de Serviços Públicos </t>
         </is>
       </c>
     </row>
@@ -2702,12 +2702,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2022NE0000517</t>
+          <t>2022NE0000516</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>12/2018</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>20014.47</v>
+        <v>718.62</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2725,19 +2725,19 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviço de fornecimento de circuito de transmissão de dados (INTERNET) -5º TA CT 001/2018. Obs. Valores destinado a cobrir despesas dos meses de maio, junho e julho de 20</t>
+          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB).- CELEBRAR 4 TERMO ADITIVO AO CONTRATO Nº.012/2018</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2022NE0000516</t>
+          <t>2022NE0000517</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>12/2018</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2746,7 +2746,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>718.62</v>
+        <v>20014.47</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2755,19 +2755,19 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB).- CELEBRAR 4 TERMO ADITIVO AO CONTRATO Nº.012/2018</t>
+          <t>Contratação para prestação de serviço de fornecimento de circuito de transmissão de dados (INTERNET) -5º TA CT 001/2018. Obs. Valores destinado a cobrir despesas dos meses de maio, junho e julho de 20</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2021NE0000368</t>
+          <t>2021NE0000370</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>12/2018</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1790.68</v>
+        <v>1137.17</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2785,19 +2785,19 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Prorrogação por 12meses da vigência do Contrato e SUPRESSÃO de 31,4499% ref. a Prestação de Serviços de Execução de Sistema de Protocolo Virtual - SPROWEB - PRODAM.</t>
+          <t>Execução do Sistema de Recursos Humanos e Folha de Pagamento do Servidor, no mês de Dezembro de 2018.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2021NE0000370</t>
+          <t>2021NE0000368</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>12/2018</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1137.17</v>
+        <v>1790.68</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2815,24 +2815,28 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Execução do Sistema de Recursos Humanos e Folha de Pagamento do Servidor, no mês de Dezembro de 2018.</t>
+          <t>Prorrogação por 12meses da vigência do Contrato e SUPRESSÃO de 31,4499% ref. a Prestação de Serviços de Execução de Sistema de Protocolo Virtual - SPROWEB - PRODAM.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025NE0000481</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr"/>
+          <t>2025NE0000482</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>4/2021</t>
+        </is>
+      </c>
       <c r="C79" t="inlineStr">
         <is>
           <t>17/10/2025</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>2589.14</v>
+        <v>2402.56</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2841,28 +2845,24 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DOS SERVIÇOS DE EXECUÇÃO DO SISTEMA PRODAM-RH PARA O CONTROLE DE CADASTRO DE PESSOAL, PROCESSAMENTO DE FOLHA DE PAGAMENTO E TRANSMISSÃO DE DADOS PARA O E-SOCIAL PARA ATENDER AS NECESSIDADE</t>
+          <t xml:space="preserve">Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação Gestor de Conteúdo Web para atender as necessidades da Agência Reguladora de Serviços Públicos </t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025NE0000482</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>4/2021</t>
-        </is>
-      </c>
+          <t>2025NE0000481</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
           <t>17/10/2025</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>2402.56</v>
+        <v>2589.14</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação Gestor de Conteúdo Web para atender as necessidades da Agência Reguladora de Serviços Públicos </t>
+          <t>CONTRATAÇÃO DOS SERVIÇOS DE EXECUÇÃO DO SISTEMA PRODAM-RH PARA O CONTROLE DE CADASTRO DE PESSOAL, PROCESSAMENTO DE FOLHA DE PAGAMENTO E TRANSMISSÃO DE DADOS PARA O E-SOCIAL PARA ATENDER AS NECESSIDADE</t>
         </is>
       </c>
     </row>
@@ -2908,12 +2908,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2022NE0000055</t>
+          <t>2022NE0000072</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2922,7 +2922,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1616.14</v>
+        <v>1895.19</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Prorrogação por 12meses da vigência do Contrato e reajuste em 32,02% ref. a Prestação de Serviços de Execução de Sistema de Cadastro de Folha de Pagamento de Pessoal - PRODAM RH. Referente o mês de fe</t>
+          <t>Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação - GERWEB - Gestor de Conteúdo Web.</t>
         </is>
       </c>
     </row>
@@ -2968,12 +2968,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2022NE0000072</t>
+          <t>2022NE0000055</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1895.19</v>
+        <v>1616.14</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -2991,21 +2991,17 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação - GERWEB - Gestor de Conteúdo Web.</t>
+          <t>Prorrogação por 12meses da vigência do Contrato e reajuste em 32,02% ref. a Prestação de Serviços de Execução de Sistema de Cadastro de Folha de Pagamento de Pessoal - PRODAM RH. Referente o mês de fe</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2023NE0000003</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>3/2017</t>
-        </is>
-      </c>
+          <t>2023NE0000004</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
           <t>17/01/2023</t>
@@ -3021,17 +3017,21 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Prorrogação por mais 12 meses de vigência do Contrato e Reajuste em 10,70%, ref. a Prestação de Execução de Sistema de Cadastro de Folha de Pagamento de Pessoal - PRODAM - RH.</t>
+          <t>Anulação do Empenho 2022NE00003 Objeto: Referente a Prestação de Serviços de Execução de Sistema de Recursos Humanos e Cadastro de Folha de Pagamento de Pessoal - PRODAM/RH; Motivo: erro formal de pre</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2023NE0000004</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr"/>
+          <t>2023NE0000003</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>3/2017</t>
+        </is>
+      </c>
       <c r="C86" t="inlineStr">
         <is>
           <t>17/01/2023</t>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Anulação do Empenho 2022NE00003 Objeto: Referente a Prestação de Serviços de Execução de Sistema de Recursos Humanos e Cadastro de Folha de Pagamento de Pessoal - PRODAM/RH; Motivo: erro formal de pre</t>
+          <t>Prorrogação por mais 12 meses de vigência do Contrato e Reajuste em 10,70%, ref. a Prestação de Execução de Sistema de Cadastro de Folha de Pagamento de Pessoal - PRODAM - RH.</t>
         </is>
       </c>
     </row>
@@ -3144,12 +3144,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2024NE0000238</t>
+          <t>2024NE0000239</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2215.57</v>
+        <v>4741.74</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3167,19 +3167,19 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação Gestor de Conteúdo Web para atender as necessidades da Agência Reguladora de Serviços Públicos </t>
+          <t>CONTRATAÇÃO DOS SERVIÇOS DE EXECUÇÃO DO SISTEMA PRODAM-RH PARA O CONTROLE DE CADASTRO DE PESSOAL, PROCESSAMENTO DE FOLHA DE PAGAMENTO E TRANSMISSÃO DE DADOS PARA O E-SOCIAL PARA ATENDER AS NECESSIDADE</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2024NE0000239</t>
+          <t>2024NE0000238</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3188,7 +3188,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>4741.74</v>
+        <v>2215.57</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DOS SERVIÇOS DE EXECUÇÃO DO SISTEMA PRODAM-RH PARA O CONTROLE DE CADASTRO DE PESSOAL, PROCESSAMENTO DE FOLHA DE PAGAMENTO E TRANSMISSÃO DE DADOS PARA O E-SOCIAL PARA ATENDER AS NECESSIDADE</t>
+          <t xml:space="preserve">Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação Gestor de Conteúdo Web para atender as necessidades da Agência Reguladora de Serviços Públicos </t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2024NE0000579</t>
+          <t>2024NE0000580</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3484,7 +3484,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>2215.57</v>
+        <v>2458.35</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3493,19 +3493,19 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação Gestor de Conteúdo Web para atender as necessidades da Agência Reguladora de Serviços Públicos </t>
+          <t>CONTRATAÇÃO DOS SERVIÇOS DE EXECUÇÃO DO SISTEMA PRODAM-RH PARA O CONTROLE DE CADASTRO DE PESSOAL, PROCESSAMENTO DE FOLHA DE PAGAMENTO E TRANSMISSÃO DE DADOS PARA O E-SOCIAL PARA ATENDER AS NECESSIDADE</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2024NE0000580</t>
+          <t>2024NE0000579</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3514,7 +3514,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>2458.35</v>
+        <v>2215.57</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DOS SERVIÇOS DE EXECUÇÃO DO SISTEMA PRODAM-RH PARA O CONTROLE DE CADASTRO DE PESSOAL, PROCESSAMENTO DE FOLHA DE PAGAMENTO E TRANSMISSÃO DE DADOS PARA O E-SOCIAL PARA ATENDER AS NECESSIDADE</t>
+          <t xml:space="preserve">Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação Gestor de Conteúdo Web para atender as necessidades da Agência Reguladora de Serviços Públicos </t>
         </is>
       </c>
     </row>
@@ -3556,7 +3556,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2015NE00146</t>
+          <t>2015NE00132</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NE Nº 132 MOTIVO ERRO FORMAL DE PREENCHIMENTO.</t>
+          <t>REFERENTE QUARTO TERMO ADITIVO AO TERMO DE CONTRATO Nº 012/2012-ARSAM</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2015NE00132</t>
+          <t>2015NE00146</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>REFERENTE QUARTO TERMO ADITIVO AO TERMO DE CONTRATO Nº 012/2012-ARSAM</t>
+          <t>ANULAÇÃO TOTAL DA NE Nº 132 MOTIVO ERRO FORMAL DE PREENCHIMENTO.</t>
         </is>
       </c>
     </row>
@@ -3676,12 +3676,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2024NE0000497</t>
+          <t>2024NE0000498</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>2458.35</v>
+        <v>2215.57</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3699,19 +3699,19 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DOS SERVIÇOS DE EXECUÇÃO DO SISTEMA PRODAM-RH PARA O CONTROLE DE CADASTRO DE PESSOAL, PROCESSAMENTO DE FOLHA DE PAGAMENTO E TRANSMISSÃO DE DADOS PARA O E-SOCIAL PARA ATENDER AS NECESSIDADE</t>
+          <t xml:space="preserve">Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação Gestor de Conteúdo Web para atender as necessidades da Agência Reguladora de Serviços Públicos </t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2024NE0000498</t>
+          <t>2024NE0000497</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3720,7 +3720,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>2215.57</v>
+        <v>2458.35</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação Gestor de Conteúdo Web para atender as necessidades da Agência Reguladora de Serviços Públicos </t>
+          <t>CONTRATAÇÃO DOS SERVIÇOS DE EXECUÇÃO DO SISTEMA PRODAM-RH PARA O CONTROLE DE CADASTRO DE PESSOAL, PROCESSAMENTO DE FOLHA DE PAGAMENTO E TRANSMISSÃO DE DADOS PARA O E-SOCIAL PARA ATENDER AS NECESSIDADE</t>
         </is>
       </c>
     </row>
@@ -3766,12 +3766,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2024NE0000568</t>
+          <t>2024NE0000569</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3780,7 +3780,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>2458.35</v>
+        <v>2215.57</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3789,19 +3789,19 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DOS SERVIÇOS DE EXECUÇÃO DO SISTEMA PRODAM-RH PARA O CONTROLE DE CADASTRO DE PESSOAL, PROCESSAMENTO DE FOLHA DE PAGAMENTO E TRANSMISSÃO DE DADOS PARA O E-SOCIAL PARA ATENDER AS NECESSIDADE</t>
+          <t xml:space="preserve">Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação Gestor de Conteúdo Web para atender as necessidades da Agência Reguladora de Serviços Públicos </t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2024NE0000569</t>
+          <t>2024NE0000568</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3810,7 +3810,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>2215.57</v>
+        <v>2458.35</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -3819,14 +3819,14 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação Gestor de Conteúdo Web para atender as necessidades da Agência Reguladora de Serviços Públicos </t>
+          <t>CONTRATAÇÃO DOS SERVIÇOS DE EXECUÇÃO DO SISTEMA PRODAM-RH PARA O CONTROLE DE CADASTRO DE PESSOAL, PROCESSAMENTO DE FOLHA DE PAGAMENTO E TRANSMISSÃO DE DADOS PARA O E-SOCIAL PARA ATENDER AS NECESSIDADE</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2023NE0000365</t>
+          <t>2023NE0000361</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>8700.440000000001</v>
+        <v>4431.14</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -3849,14 +3849,14 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação - GERWEB - Gestor de Conteúdo Web. Parecer jurídico nº 115/2022-ASJUR/ARSEPAM de 17/05/2022. TC</t>
+          <t xml:space="preserve">Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação Gestor de Conteúdo Web para atender as necessidades da Agência Reguladora de Serviços Públicos </t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2023NE0000361</t>
+          <t>2023NE0000365</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3870,7 +3870,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>4431.14</v>
+        <v>8700.440000000001</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -3879,19 +3879,19 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação Gestor de Conteúdo Web para atender as necessidades da Agência Reguladora de Serviços Públicos </t>
+          <t>Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação - GERWEB - Gestor de Conteúdo Web. Parecer jurídico nº 115/2022-ASJUR/ARSEPAM de 17/05/2022. TC</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2022NE0000130</t>
+          <t>2022NE0000139</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3900,7 +3900,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>13342.98</v>
+        <v>7580.76</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -3909,19 +3909,19 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviço de fornecimento de circuito de transmissão de dados (INTERNET). MESES DE MARÇO E ABRIL</t>
+          <t>Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação - GERWEB - Gestor de Conteúdo Web.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2022NE0000132</t>
+          <t>2022NE0000129</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>12/2018</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>7007.04</v>
+        <v>9696.84</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -3939,19 +3939,19 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB).</t>
+          <t>Prorrogação por 12meses da vigência do Contrato e reajuste em 32,02% ref. a Prestação de Serviços de Execução de Sistema de Cadastro de Folha de Pagamento de Pessoal - PRODAM RH.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2022NE0000129</t>
+          <t>2022NE0000132</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>12/2018</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3960,7 +3960,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>9696.84</v>
+        <v>7007.04</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -3969,19 +3969,19 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Prorrogação por 12meses da vigência do Contrato e reajuste em 32,02% ref. a Prestação de Serviços de Execução de Sistema de Cadastro de Folha de Pagamento de Pessoal - PRODAM RH.</t>
+          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2022NE0000139</t>
+          <t>2022NE0000130</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3990,7 +3990,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>7580.76</v>
+        <v>13342.98</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação - GERWEB - Gestor de Conteúdo Web.</t>
+          <t>Contratação para prestação de serviço de fornecimento de circuito de transmissão de dados (INTERNET). MESES DE MARÇO E ABRIL</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026NE0000003</t>
+          <t>2026NE0000002</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>10356.56</v>
+        <v>9610.24</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4059,19 +4059,19 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DOS SERVIÇOS DE EXECUÇÃO DO SISTEMA PRODAM-RH PARA O CONTROLE DE CADASTRO DE PESSOAL, PROCESSAMENTO DE FOLHA DE PAGAMENTO E TRANSMISSÃO DE DADOS PARA O E-SOCIAL PARA ATENDER AS NECESSIDADE</t>
+          <t xml:space="preserve">Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação Gestor de Conteúdo Web para atender as necessidades da Agência Reguladora de Serviços Públicos </t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026NE0000002</t>
+          <t>2026NE0000003</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4080,7 +4080,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>9610.24</v>
+        <v>10356.56</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4089,19 +4089,19 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação Gestor de Conteúdo Web para atender as necessidades da Agência Reguladora de Serviços Públicos </t>
+          <t>CONTRATAÇÃO DOS SERVIÇOS DE EXECUÇÃO DO SISTEMA PRODAM-RH PARA O CONTROLE DE CADASTRO DE PESSOAL, PROCESSAMENTO DE FOLHA DE PAGAMENTO E TRANSMISSÃO DE DADOS PARA O E-SOCIAL PARA ATENDER AS NECESSIDADE</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2015NE00010</t>
+          <t>2015NE00006</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>12/2012</t>
+          <t>6/2014</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4110,7 +4110,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>7422.8</v>
+        <v>85800</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4126,12 +4126,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2015NE00006</t>
+          <t>2015NE00010</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>6/2014</t>
+          <t>12/2012</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4140,7 +4140,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>85800</v>
+        <v>7422.8</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4156,12 +4156,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2025NE0000529</t>
+          <t>2025NE0000535</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4170,7 +4170,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>2589.14</v>
+        <v>2402.56</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4179,19 +4179,19 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DOS SERVIÇOS DE EXECUÇÃO DO SISTEMA PRODAM-RH PARA O CONTROLE DE CADASTRO DE PESSOAL, PROCESSAMENTO DE FOLHA DE PAGAMENTO E TRANSMISSÃO DE DADOS PARA O E-SOCIAL PARA ATENDER AS NECESSIDADE</t>
+          <t xml:space="preserve">Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação Gestor de Conteúdo Web para atender as necessidades da Agência Reguladora de Serviços Públicos </t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2025NE0000535</t>
+          <t>2025NE0000529</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>2402.56</v>
+        <v>2589.14</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4209,19 +4209,19 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação Gestor de Conteúdo Web para atender as necessidades da Agência Reguladora de Serviços Públicos </t>
+          <t>CONTRATAÇÃO DOS SERVIÇOS DE EXECUÇÃO DO SISTEMA PRODAM-RH PARA O CONTROLE DE CADASTRO DE PESSOAL, PROCESSAMENTO DE FOLHA DE PAGAMENTO E TRANSMISSÃO DE DADOS PARA O E-SOCIAL PARA ATENDER AS NECESSIDADE</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2015NE00039</t>
+          <t>2015NE00041</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>6/2014</t>
+          <t>12/2012</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4230,7 +4230,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>60840</v>
+        <v>5853.71</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4246,12 +4246,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2015NE00041</t>
+          <t>2015NE00039</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>12/2012</t>
+          <t>6/2014</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4260,7 +4260,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>5853.71</v>
+        <v>60840</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2021NE0000027</t>
+          <t>2021NE0000019</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -4316,7 +4316,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>13506.6</v>
+        <v>3407.26</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE ACESSO A REDE MUNDIAL DE COMPUTADORES (INTERNET)</t>
+          <t>Contratação de Prestação de Serviços de protocolo em sistema de plataforma web - SPROWEB.</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2021NE0000019</t>
+          <t>2021NE0000027</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>3407.26</v>
+        <v>13506.6</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4377,19 +4377,19 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Contratação de Prestação de Serviços de protocolo em sistema de plataforma web - SPROWEB.</t>
+          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE ACESSO A REDE MUNDIAL DE COMPUTADORES (INTERNET)</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2016NE00027</t>
+          <t>2016NE00029</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>6/2014</t>
+          <t>12/2012</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4398,7 +4398,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>71968</v>
+        <v>6364.33</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4407,19 +4407,19 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇO DE ACESSO A INTERNET - PRORROGAÇÃO DE PRAZO POR MAIS 12 MESES</t>
+          <t>PRESTAÇÃO DE SERVIÇO DE EXECUÇÃO DO SISTEMA CAD FOLHA CFPP - PRORROGAÇÃO DE PRAZO 12 MESES E REEQUILÍBRIO FINANCEIRO</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2016NE00029</t>
+          <t>2016NE00027</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>12/2012</t>
+          <t>6/2014</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4428,7 +4428,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>6364.33</v>
+        <v>71968</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4437,19 +4437,19 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇO DE EXECUÇÃO DO SISTEMA CAD FOLHA CFPP - PRORROGAÇÃO DE PRAZO 12 MESES E REEQUILÍBRIO FINANCEIRO</t>
+          <t>PRESTAÇÃO DE SERVIÇO DE ACESSO A INTERNET - PRORROGAÇÃO DE PRAZO POR MAIS 12 MESES</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2025NE0000599</t>
+          <t>2025NE0000598</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4458,7 +4458,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>2589.14</v>
+        <v>2402.56</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4467,19 +4467,19 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DOS SERVIÇOS DE EXECUÇÃO DO SISTEMA PRODAM-RH PARA O CONTROLE DE CADASTRO DE PESSOAL, PROCESSAMENTO DE FOLHA DE PAGAMENTO E TRANSMISSÃO DE DADOS PARA O E-SOCIAL PARA ATENDER AS NECESSIDADE</t>
+          <t xml:space="preserve">Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação Gestor de Conteúdo Web para atender as necessidades da Agência Reguladora de Serviços Públicos </t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2025NE0000598</t>
+          <t>2025NE0000599</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4488,7 +4488,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>2402.56</v>
+        <v>2589.14</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4497,19 +4497,19 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação Gestor de Conteúdo Web para atender as necessidades da Agência Reguladora de Serviços Públicos </t>
+          <t>CONTRATAÇÃO DOS SERVIÇOS DE EXECUÇÃO DO SISTEMA PRODAM-RH PARA O CONTROLE DE CADASTRO DE PESSOAL, PROCESSAMENTO DE FOLHA DE PAGAMENTO E TRANSMISSÃO DE DADOS PARA O E-SOCIAL PARA ATENDER AS NECESSIDADE</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2022NE0000463</t>
+          <t>2022NE0000472</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4518,7 +4518,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1789.07</v>
+        <v>2175.11</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Contratação de Prestação de Serviços referente a Execução de sistema de cadastro de folha de pagamento de Pessoal - Prodam/RH com reajuste de 10,70% e Prorrogação de vigência por 12 meses.</t>
+          <t>Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação - GERWEB - Gestor de Conteúdo Web.</t>
         </is>
       </c>
     </row>
@@ -4564,12 +4564,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2022NE0000472</t>
+          <t>2022NE0000463</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>2175.11</v>
+        <v>1789.07</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4587,19 +4587,19 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação - GERWEB - Gestor de Conteúdo Web.</t>
+          <t>Contratação de Prestação de Serviços referente a Execução de sistema de cadastro de folha de pagamento de Pessoal - Prodam/RH com reajuste de 10,70% e Prorrogação de vigência por 12 meses.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2022NE0000041</t>
+          <t>2022NE0000045</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4608,7 +4608,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1616.14</v>
+        <v>1895.19</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4617,19 +4617,19 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Prorrogação por 12meses da vigência do Contrato e reajuste em 32,02% ref. a Prestação de Serviços de Execução de Sistema de Cadastro de Folha de Pagamento de Pessoal - PRODAM RH.</t>
+          <t>Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação - GERWEB - Gestor de Conteúdo Web.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2022NE0000045</t>
+          <t>2022NE0000041</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1895.19</v>
+        <v>1616.14</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4647,19 +4647,19 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação - GERWEB - Gestor de Conteúdo Web.</t>
+          <t>Prorrogação por 12meses da vigência do Contrato e reajuste em 32,02% ref. a Prestação de Serviços de Execução de Sistema de Cadastro de Folha de Pagamento de Pessoal - PRODAM RH.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2024NE0000342</t>
+          <t>2024NE0000343</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4668,7 +4668,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>4431.14</v>
+        <v>4741.74</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4677,19 +4677,19 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação Gestor de Conteúdo Web para atender as necessidades da Agência Reguladora de Serviços Públicos </t>
+          <t>CONTRATAÇÃO DOS SERVIÇOS DE EXECUÇÃO DO SISTEMA PRODAM-RH PARA O CONTROLE DE CADASTRO DE PESSOAL, PROCESSAMENTO DE FOLHA DE PAGAMENTO E TRANSMISSÃO DE DADOS PARA O E-SOCIAL PARA ATENDER AS NECESSIDADE</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2024NE0000343</t>
+          <t>2024NE0000342</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4698,7 +4698,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>4741.74</v>
+        <v>4431.14</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DOS SERVIÇOS DE EXECUÇÃO DO SISTEMA PRODAM-RH PARA O CONTROLE DE CADASTRO DE PESSOAL, PROCESSAMENTO DE FOLHA DE PAGAMENTO E TRANSMISSÃO DE DADOS PARA O E-SOCIAL PARA ATENDER AS NECESSIDADE</t>
+          <t xml:space="preserve">Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação Gestor de Conteúdo Web para atender as necessidades da Agência Reguladora de Serviços Públicos </t>
         </is>
       </c>
     </row>
@@ -4744,12 +4744,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2025NE0000006</t>
+          <t>2025NE0000005</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4758,7 +4758,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>4916.7</v>
+        <v>4431.14</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -4767,19 +4767,19 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DOS SERVIÇOS DE EXECUÇÃO DO SISTEMA PRODAM-RH PARA O CONTROLE DE CADASTRO DE PESSOAL, PROCESSAMENTO DE FOLHA DE PAGAMENTO E TRANSMISSÃO DE DADOS PARA O E-SOCIAL PARA ATENDER AS NECESSIDADE</t>
+          <t xml:space="preserve">Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação Gestor de Conteúdo Web para atender as necessidades da Agência Reguladora de Serviços Públicos </t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2025NE0000005</t>
+          <t>2025NE0000006</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4788,7 +4788,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>4431.14</v>
+        <v>4916.7</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -4797,19 +4797,19 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação Gestor de Conteúdo Web para atender as necessidades da Agência Reguladora de Serviços Públicos </t>
+          <t>CONTRATAÇÃO DOS SERVIÇOS DE EXECUÇÃO DO SISTEMA PRODAM-RH PARA O CONTROLE DE CADASTRO DE PESSOAL, PROCESSAMENTO DE FOLHA DE PAGAMENTO E TRANSMISSÃO DE DADOS PARA O E-SOCIAL PARA ATENDER AS NECESSIDADE</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2024NE0000005</t>
+          <t>2024NE0000003</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>4741.74</v>
+        <v>4431.14</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -4827,19 +4827,19 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DOS SERVIÇOS DE EXECUÇÃO DO SISTEMA PRODAM-RH PARA O CONTROLE DE CADASTRO DE PESSOAL, PROCESSAMENTO DE FOLHA DE PAGAMENTO E TRANSMISSÃO DE DADOS PARA O E-SOCIAL PARA ATENDER AS NECESSIDADE</t>
+          <t xml:space="preserve">Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação Gestor de Conteúdo Web para atender as necessidades da Agência Reguladora de Serviços Públicos </t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2024NE0000003</t>
+          <t>2024NE0000005</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4848,7 +4848,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>4431.14</v>
+        <v>4741.74</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -4857,19 +4857,19 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Empresa Especializada na prestação de serviços de Licença de uso de sistema de informação Gestor de Conteúdo Web para atender as necessidades da Agência Reguladora de Serviços Públicos </t>
+          <t>CONTRATAÇÃO DOS SERVIÇOS DE EXECUÇÃO DO SISTEMA PRODAM-RH PARA O CONTROLE DE CADASTRO DE PESSOAL, PROCESSAMENTO DE FOLHA DE PAGAMENTO E TRANSMISSÃO DE DADOS PARA O E-SOCIAL PARA ATENDER AS NECESSIDADE</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2023NE0000010</t>
+          <t>2023NE0000009</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>12/2018</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4878,7 +4878,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1268.16</v>
+        <v>1789.07</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB).</t>
+          <t>Prorrogação por mais 12 meses de vigência do Contrato e Reajuste em 10,70%, ref. a Prestação de Execução de Sistema de Cadastro de Folha de Pagamento de Pessoal - PRODAM - RH.</t>
         </is>
       </c>
     </row>
@@ -4924,12 +4924,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2023NE0000009</t>
+          <t>2023NE0000010</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>12/2018</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4938,7 +4938,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1789.07</v>
+        <v>1268.16</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -4947,17 +4947,21 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Prorrogação por mais 12 meses de vigência do Contrato e Reajuste em 10,70%, ref. a Prestação de Execução de Sistema de Cadastro de Folha de Pagamento de Pessoal - PRODAM - RH.</t>
+          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2020NE00022</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr"/>
+          <t>2020NE00005</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>3/2017</t>
+        </is>
+      </c>
       <c r="C151" t="inlineStr">
         <is>
           <t>02/01/2020</t>
@@ -4973,24 +4977,28 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NE: 05 MOTIVO: ERRO FORMAL DE PREENCHIMENTO.</t>
+          <t>Contratação para prestação de serviços de execução do Sistema de Cadastro e Folha de Pagamento de Pessoal - PRODAM-RH.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2020NE00025</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr"/>
+          <t>2020NE00030</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>3/2017</t>
+        </is>
+      </c>
       <c r="C152" t="inlineStr">
         <is>
           <t>02/01/2020</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>22499.7</v>
+        <v>3672.48</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -4999,19 +5007,19 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Anulação da NE nº. 016/2020 Motivo: Erro formal de preenchimento</t>
+          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMA DE CADASTRO E FOLHA DE PAGAMENTO DE PESSOAL - PRODAM-RH</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2020NE00011</t>
+          <t>2020NE00033</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>12/2018</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5020,7 +5028,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>4677.3</v>
+        <v>22499.7</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5029,7 +5037,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Contratação de Prestação de Serviços de Sistema de Protocolo em Plataforma Web - SPROWEB.</t>
+          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE ACESSO A REDE MUNDIAL DE COMPUTADORES (INTERNET).</t>
         </is>
       </c>
     </row>
@@ -5066,12 +5074,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2020NE00033</t>
+          <t>2020NE00011</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>12/2018</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5080,7 +5088,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>22499.7</v>
+        <v>4677.3</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5089,28 +5097,24 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE ACESSO A REDE MUNDIAL DE COMPUTADORES (INTERNET).</t>
+          <t>Contratação de Prestação de Serviços de Sistema de Protocolo em Plataforma Web - SPROWEB.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2020NE00030</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>3/2017</t>
-        </is>
-      </c>
+          <t>2020NE00025</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr">
         <is>
           <t>02/01/2020</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>3672.48</v>
+        <v>22499.7</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5119,21 +5123,17 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMA DE CADASTRO E FOLHA DE PAGAMENTO DE PESSOAL - PRODAM-RH</t>
+          <t>Anulação da NE nº. 016/2020 Motivo: Erro formal de preenchimento</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2020NE00005</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>3/2017</t>
-        </is>
-      </c>
+          <t>2020NE00022</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr">
         <is>
           <t>02/01/2020</t>
@@ -5149,19 +5149,19 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de execução do Sistema de Cadastro e Folha de Pagamento de Pessoal - PRODAM-RH.</t>
+          <t>ANULAÇÃO DA NE: 05 MOTIVO: ERRO FORMAL DE PREENCHIMENTO.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2019NE00008</t>
+          <t>2019NE00002</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>12/2018</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>21764.04</v>
+        <v>4677.3</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO de Serviços de Acesso a Internet - conexão dedicada a rede mundial de computadores, conforme as especificações descritas no Projeto Básico.</t>
+          <t>Contratação de Prestação de Serviços de PROTOCOLO em Sistema de Plataforma SPROWEB.</t>
         </is>
       </c>
     </row>
@@ -5216,12 +5216,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2019NE00002</t>
+          <t>2019NE00008</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>12/2018</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5230,7 +5230,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>4677.3</v>
+        <v>21764.04</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -5239,19 +5239,19 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Contratação de Prestação de Serviços de PROTOCOLO em Sistema de Plataforma SPROWEB.</t>
+          <t>CONTRATAÇÃO de Serviços de Acesso a Internet - conexão dedicada a rede mundial de computadores, conforme as especificações descritas no Projeto Básico.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2018NE00020</t>
+          <t>2018NE00018</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>1/2018</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>8724.799999999999</v>
+        <v>79106.03999999999</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -5269,19 +5269,19 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Prestação de Serviço de Processamento de Dados referente ao sistema PRODAM/ RH.</t>
+          <t>Contratação de Prestação de Serviço de Acesso a Internet</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2018NE00018</t>
+          <t>2018NE00020</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>1/2018</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5290,7 +5290,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>79106.03999999999</v>
+        <v>8724.799999999999</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5299,19 +5299,19 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Contratação de Prestação de Serviço de Acesso a Internet</t>
+          <t>Prestação de Serviço de Processamento de Dados referente ao sistema PRODAM/ RH.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2017NE00048</t>
+          <t>2017NE00051</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>12/2012</t>
+          <t>6/2014</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5320,7 +5320,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>7635.78</v>
+        <v>79291.91</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5329,19 +5329,19 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>REFERENTE AO QUINTO TERMO ADITIVO CONTRATO Nº 012/2012, CFPP CADASTRO E FOLHA DE PAGAMENTO PESSOAL, COM VIGÊNCIA DE 12.09.2016 A 11.09.2017. VALOR MENSAL É R$ 848,42(oitocentos e quarenta e oito reais</t>
+          <t>REFERENTE AO TERCEIRO TERMO ADITIVO AO CONTRATO 006/2014, SERVIÇO DE ACESSO À REDE MUNDIAL DE COMPUTADORES,ATRAVÉS DO CONTRATO Nº 006/2014. VALOR MENSAL É DE R$ 6.905,81(seis mil novecentos e cinco re</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2017NE00051</t>
+          <t>2017NE00048</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>6/2014</t>
+          <t>12/2012</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5350,7 +5350,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>79291.91</v>
+        <v>7635.78</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5359,14 +5359,14 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>REFERENTE AO TERCEIRO TERMO ADITIVO AO CONTRATO 006/2014, SERVIÇO DE ACESSO À REDE MUNDIAL DE COMPUTADORES,ATRAVÉS DO CONTRATO Nº 006/2014. VALOR MENSAL É DE R$ 6.905,81(seis mil novecentos e cinco re</t>
+          <t>REFERENTE AO QUINTO TERMO ADITIVO CONTRATO Nº 012/2012, CFPP CADASTRO E FOLHA DE PAGAMENTO PESSOAL, COM VIGÊNCIA DE 12.09.2016 A 11.09.2017. VALOR MENSAL É R$ 848,42(oitocentos e quarenta e oito reais</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2019NE00421</t>
+          <t>2019NE00420</t>
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>817.95</v>
+        <v>392.12</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NE Nº. 002/2019 REFERENTE AO CONTRATO Nº. 12/2018 - PROTOCOLO EM SISTEMA DE PLATAFORMA SPROWEB EM ATENÇÃO AO CELEBRAÇÃO DO TERMO ADITIVO E ENCERRAMENTO DO EXERCÍCIO.</t>
+          <t>ANULAÇÃO DO SALDO DA NE Nº. 001/2019 REFERENTE AO PRIMEIRO TERMO ADITIVO AO CONTRATO Nº. 03/2017 - PRODAM-RH EM ATENÇÃO AO CELEBRAÇÃO DO NOVO ADITIVO E ENCERRAMENTO DO EXERCÍCIO.</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2019NE00420</t>
+          <t>2019NE00421</t>
         </is>
       </c>
       <c r="B167" t="inlineStr"/>
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>392.12</v>
+        <v>817.95</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NE Nº. 001/2019 REFERENTE AO PRIMEIRO TERMO ADITIVO AO CONTRATO Nº. 03/2017 - PRODAM-RH EM ATENÇÃO AO CELEBRAÇÃO DO NOVO ADITIVO E ENCERRAMENTO DO EXERCÍCIO.</t>
+          <t>ANULAÇÃO DO SALDO DA NE Nº. 002/2019 REFERENTE AO CONTRATO Nº. 12/2018 - PROTOCOLO EM SISTEMA DE PLATAFORMA SPROWEB EM ATENÇÃO AO CELEBRAÇÃO DO TERMO ADITIVO E ENCERRAMENTO DO EXERCÍCIO.</t>
         </is>
       </c>
     </row>
